--- a/datasets/tenant-inputs/templates/universal/standard-2026-07-v3/00_enterprise_profile.xlsx
+++ b/datasets/tenant-inputs/templates/universal/standard-2026-07-v3/00_enterprise_profile.xlsx
@@ -2,7 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R1aefd4fa985c48c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="7" r:id="RabarvaStartHereGoverned"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet Guide" sheetId="1" r:id="R1aefd4fa985c48c9"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R137bd1bc59f446f8"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R981986f1333c4b87"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R24edf48ca2d24a74"/>
@@ -615,6 +616,251 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/abarvaStartHere.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="104" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00 Enterprise Profile — Start Here</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This is one of the internal target templates AbarVa fills in. You do not have to complete it by hand — it is here so you can see exactly what we are trying to learn and check that we got it right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">About this workbook</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What this workbook is</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A canonical target template. AbarVa populates it from your extracts, documents, and interviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Client-facing workstream(s)</t>
+        </is>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">WS01 Enterprise Strategy and Operating Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who normally provides this</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CEO strategy; COO; CIO; enterprise transformation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What usually populates it</t>
+        </is>
+      </c>
+      <c r="B8" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">strategy documents; operating model; business unit list; business priorities; capability model if available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source extract templates that help</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None. Provide the exports and documents listed above in whatever native format your systems produce.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Canonical target file</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00_enterprise_profile.csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What to do</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 1</t>
+        </is>
+      </c>
+      <c r="B13" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Open AbarVa_Template_Pack_Index_v3.xlsx first. Its Intake Workstreams and Review Queue sheets show the whole picture and who owns each part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 2</t>
+        </is>
+      </c>
+      <c r="B14" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Send us the exports and documents listed above. AbarVa maps them into this template so your team is not filling in 19 files by hand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 3</t>
+        </is>
+      </c>
+      <c r="B15" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use the Sheet Guide tab for a description of every other tab in this workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 4</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review what we produce and tell us where it is wrong. Anything you cannot confirm should be left open as a gap rather than guessed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Step 5</t>
+        </is>
+      </c>
+      <c r="B17" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Record your review decision in the SME Review Matrix in AbarVa_Template_Pack_Index_v3.xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before any of this is used</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed gates</t>
+        </is>
+      </c>
+      <c r="B20" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This workbook is a template and review artifact. Completing it does not load data into any database, index retrieval, enable aVa or any product surface, or make its content client truth. SME validation and the promotion gates come first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What your SMEs confirm</t>
+        </is>
+      </c>
+      <c r="B21" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm business model, capability labels, strategic priorities, and which generated profiles match client language.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evidence we need with the data</t>
+        </is>
+      </c>
+      <c r="B22" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Source system, report or export name, who owns it, when it was pulled, the period it covers, whether it is full or partial, and any known limitations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Governance reference</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">docs/governance/CLIENT_REVIEW_WORKBOOK_QUALITY_BAR.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
